--- a/Ebenezer Real Time Monitoring Online.xlsx
+++ b/Ebenezer Real Time Monitoring Online.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cranfield-my.sharepoint.com/personal/andrews_kwakye_cranfield_ac_uk/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="8_{E586AC2C-623F-4E64-9CD9-DB85A9D96993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC69978-704A-4AE6-BB23-31979CCB3B41}"/>
+  <xr:revisionPtr revIDLastSave="326" documentId="8_{E586AC2C-623F-4E64-9CD9-DB85A9D96993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4959305E-D338-4745-9E83-4DA4A04DFF30}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="325">
   <si>
     <t>Care Data Services — Multi-Facility Tracker</t>
   </si>
@@ -460,9 +460,6 @@
     <t>EXP-002</t>
   </si>
   <si>
-    <t>Utilities</t>
-  </si>
-  <si>
     <t>Gas bill</t>
   </si>
   <si>
@@ -499,9 +496,6 @@
     <t>EXP-005</t>
   </si>
   <si>
-    <t>Consumables</t>
-  </si>
-  <si>
     <t>Incontinence supplies</t>
   </si>
   <si>
@@ -511,9 +505,6 @@
     <t>EXP-006</t>
   </si>
   <si>
-    <t>Training</t>
-  </si>
-  <si>
     <t>Moving and handling refresh</t>
   </si>
   <si>
@@ -992,6 +983,45 @@
   </si>
   <si>
     <t>DOLS Team</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Telephone</t>
+  </si>
+  <si>
+    <t>Council Tax</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>EXP-007</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>Amazon order</t>
+  </si>
+  <si>
+    <t>EXP-008</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Gloves</t>
   </si>
 </sst>
 </file>
@@ -1162,7 +1192,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1185,12 +1215,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D1C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D1C7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1282,6 +1323,9 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1314,6 +1358,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1514,10 +1561,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1708,10 +1751,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="33"/>
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -1908,44 +1951,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
     </row>
     <row r="3" spans="1:16" ht="26" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
@@ -1996,19 +2039,19 @@
         <v>50</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G4" s="7">
         <v>7908661708</v>
@@ -2040,19 +2083,19 @@
         <v>55</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G5" s="7">
         <v>7908661708</v>
@@ -2084,19 +2127,19 @@
         <v>58</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G6" s="7">
         <v>7908661708</v>
@@ -2125,22 +2168,22 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G7" s="7">
         <v>7908661708</v>
@@ -2165,22 +2208,22 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G8" s="7">
         <v>7908661708</v>
@@ -2205,22 +2248,22 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G9" s="7">
         <v>7908661708</v>
@@ -2245,22 +2288,22 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C10" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>191</v>
-      </c>
       <c r="E10" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G10" s="7">
         <v>7908661708</v>
@@ -2285,22 +2328,22 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="31" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B11" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="E11" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="F11" s="32" t="s">
         <v>190</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>193</v>
       </c>
       <c r="G11" s="7">
         <v>7908661708</v>
@@ -2373,44 +2416,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -2464,7 +2507,7 @@
         <v>73</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>50</v>
@@ -2487,7 +2530,7 @@
         <v>75</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>70</v>
@@ -2496,7 +2539,7 @@
         <v>1200</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>76</v>
@@ -2511,7 +2554,7 @@
         <v>77</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>50</v>
@@ -2534,7 +2577,7 @@
         <v>79</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>70</v>
@@ -2543,7 +2586,7 @@
         <v>1650</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M5" s="9" t="s">
         <v>76</v>
@@ -2558,7 +2601,7 @@
         <v>80</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>50</v>
@@ -2581,7 +2624,7 @@
         <v>75</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>70</v>
@@ -2590,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>54</v>
@@ -2605,7 +2648,7 @@
         <v>82</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>50</v>
@@ -2619,7 +2662,7 @@
       </c>
       <c r="F7" s="9">
         <f ca="1">IFERROR(DATEDIF(E7,TODAY(),"Y"),"")</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>83</v>
@@ -2628,7 +2671,7 @@
         <v>79</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>70</v>
@@ -2637,7 +2680,7 @@
         <v>1100</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>76</v>
@@ -2649,10 +2692,10 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>55</v>
@@ -2672,13 +2715,13 @@
         <v>75</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>54</v>
@@ -2686,10 +2729,10 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>55</v>
@@ -2703,19 +2746,19 @@
       </c>
       <c r="F9" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
         <v>79</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>54</v>
@@ -2723,10 +2766,10 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>55</v>
@@ -2740,19 +2783,19 @@
       </c>
       <c r="F10" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" t="s">
         <v>75</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>54</v>
@@ -2760,10 +2803,10 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>55</v>
@@ -2783,13 +2826,13 @@
         <v>79</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N11" s="7" t="s">
         <v>54</v>
@@ -2797,10 +2840,10 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>55</v>
@@ -2820,13 +2863,13 @@
         <v>75</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N12" s="7" t="s">
         <v>54</v>
@@ -2834,10 +2877,10 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -2857,13 +2900,13 @@
         <v>79</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N13" s="7" t="s">
         <v>54</v>
@@ -2871,10 +2914,10 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>58</v>
@@ -2894,13 +2937,13 @@
         <v>79</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N14" s="7" t="s">
         <v>54</v>
@@ -2908,10 +2951,10 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -2931,13 +2974,13 @@
         <v>79</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>54</v>
@@ -2945,10 +2988,10 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>58</v>
@@ -2968,13 +3011,13 @@
         <v>75</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N16" s="7" t="s">
         <v>54</v>
@@ -2982,13 +3025,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D17" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C17,Facilities!A:A,0)),"")</f>
@@ -3005,13 +3048,13 @@
         <v>75</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>54</v>
@@ -3019,13 +3062,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D18" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C18,Facilities!A:A,0)),"")</f>
@@ -3036,19 +3079,19 @@
       </c>
       <c r="F18" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H18" t="s">
         <v>79</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>54</v>
@@ -3056,13 +3099,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D19" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C19,Facilities!A:A,0)),"")</f>
@@ -3079,13 +3122,13 @@
         <v>79</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N19" s="7" t="s">
         <v>54</v>
@@ -3093,13 +3136,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D20" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C20,Facilities!A:A,0)),"")</f>
@@ -3116,13 +3159,13 @@
         <v>75</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N20" s="7" t="s">
         <v>54</v>
@@ -3130,13 +3173,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D21" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C21,Facilities!A:A,0)),"")</f>
@@ -3153,13 +3196,13 @@
         <v>79</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N21" s="7" t="s">
         <v>54</v>
@@ -3167,13 +3210,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D22" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C22,Facilities!A:A,0)),"")</f>
@@ -3190,13 +3233,13 @@
         <v>75</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N22" s="7" t="s">
         <v>54</v>
@@ -3204,13 +3247,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D23" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C23,Facilities!A:A,0)),"")</f>
@@ -3227,13 +3270,13 @@
         <v>79</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N23" s="7" t="s">
         <v>54</v>
@@ -3241,13 +3284,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D24" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C24,Facilities!A:A,0)),"")</f>
@@ -3264,13 +3307,13 @@
         <v>79</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N24" s="7" t="s">
         <v>54</v>
@@ -3278,13 +3321,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D25" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C25,Facilities!A:A,0)),"")</f>
@@ -3295,19 +3338,19 @@
       </c>
       <c r="F25" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H25" t="s">
         <v>79</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>54</v>
@@ -3315,13 +3358,13 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D26" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C26,Facilities!A:A,0)),"")</f>
@@ -3338,13 +3381,13 @@
         <v>75</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N26" s="7" t="s">
         <v>54</v>
@@ -3352,13 +3395,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D27" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C27,Facilities!A:A,0)),"")</f>
@@ -3375,13 +3418,13 @@
         <v>79</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N27" s="7" t="s">
         <v>54</v>
@@ -3389,13 +3432,13 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D28" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C28,Facilities!A:A,0)),"")</f>
@@ -3406,19 +3449,19 @@
       </c>
       <c r="F28" s="9">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s">
         <v>79</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N28" s="7" t="s">
         <v>54</v>
@@ -3426,13 +3469,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D29" s="7" t="str">
         <f>IFERROR(INDEX(Facilities!B:B,MATCH(C29,Facilities!A:A,0)),"")</f>
@@ -3449,13 +3492,13 @@
         <v>75</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="N29" s="7" t="s">
         <v>54</v>
@@ -3506,44 +3549,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -3594,7 +3637,7 @@
         <v>73</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>50</v>
@@ -3613,7 +3656,7 @@
       </c>
       <c r="I4" s="7">
         <f ca="1">IFERROR(H4-TODAY(),"")</f>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J4" s="13" t="str">
         <f t="shared" ref="J4:J8" ca="1" si="0">IFERROR(IF(H4="","",IF(H4&lt;TODAY(),"OVERDUE",IF(H4-TODAY()&lt;=14,"Expires in 14 days",IF(H4-TODAY()&lt;=30,"Due within 30 days","On track")))),"On track")</f>
@@ -3635,7 +3678,7 @@
         <v>77</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>50</v>
@@ -3654,7 +3697,7 @@
       </c>
       <c r="I5" s="9">
         <f ca="1">IFERROR(H5-TODAY(),"")</f>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J5" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3678,7 +3721,7 @@
         <v>80</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>50</v>
@@ -3697,7 +3740,7 @@
       </c>
       <c r="I6" s="7">
         <f ca="1">IFERROR(H6-TODAY(),"")</f>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J6" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3719,7 +3762,7 @@
         <v>82</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>50</v>
@@ -3738,7 +3781,7 @@
       </c>
       <c r="I7" s="9">
         <f ca="1">IFERROR(H7-TODAY(),"")</f>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J7" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3757,10 +3800,10 @@
         <v>104</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>55</v>
@@ -3779,7 +3822,7 @@
       </c>
       <c r="I8" s="7">
         <f ca="1">IFERROR(H8-TODAY(),"")</f>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J8" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3795,13 +3838,13 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>55</v>
@@ -3820,14 +3863,14 @@
       </c>
       <c r="I9" s="7">
         <f t="shared" ref="I9:I29" ca="1" si="1">IFERROR(H9-TODAY(),"")</f>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J9" s="13" t="str">
         <f t="shared" ref="J9:J29" ca="1" si="2">IFERROR(IF(H9="","",IF(H9&lt;TODAY(),"OVERDUE",IF(H9-TODAY()&lt;=14,"Expires in 14 days",IF(H9-TODAY()&lt;=30,"Due within 30 days","On track")))),"On track")</f>
         <v>On track</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>54</v>
@@ -3836,13 +3879,13 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>55</v>
@@ -3861,14 +3904,14 @@
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>54</v>
@@ -3877,13 +3920,13 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>55</v>
@@ -3902,14 +3945,14 @@
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J11" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>54</v>
@@ -3918,13 +3961,13 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>55</v>
@@ -3943,14 +3986,14 @@
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J12" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>54</v>
@@ -3959,13 +4002,13 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>58</v>
@@ -3984,14 +4027,14 @@
       </c>
       <c r="I13" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J13" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>54</v>
@@ -4000,13 +4043,13 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>58</v>
@@ -4025,14 +4068,14 @@
       </c>
       <c r="I14" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J14" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>54</v>
@@ -4041,13 +4084,13 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>58</v>
@@ -4066,14 +4109,14 @@
       </c>
       <c r="I15" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J15" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>54</v>
@@ -4082,13 +4125,13 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>58</v>
@@ -4107,14 +4150,14 @@
       </c>
       <c r="I16" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J16" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>54</v>
@@ -4123,22 +4166,22 @@
     </row>
     <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G17" s="10">
         <v>46100</v>
@@ -4148,14 +4191,14 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J17" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>76</v>
@@ -4164,22 +4207,22 @@
     </row>
     <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G18" s="10">
         <v>46100</v>
@@ -4189,14 +4232,14 @@
       </c>
       <c r="I18" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J18" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>76</v>
@@ -4205,22 +4248,22 @@
     </row>
     <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G19" s="10">
         <v>46100</v>
@@ -4230,14 +4273,14 @@
       </c>
       <c r="I19" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>76</v>
@@ -4246,22 +4289,22 @@
     </row>
     <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G20" s="10">
         <v>46100</v>
@@ -4271,14 +4314,14 @@
       </c>
       <c r="I20" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>76</v>
@@ -4287,22 +4330,22 @@
     </row>
     <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G21" s="10">
         <v>46100</v>
@@ -4312,14 +4355,14 @@
       </c>
       <c r="I21" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>76</v>
@@ -4328,22 +4371,22 @@
     </row>
     <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G22" s="10">
         <v>46100</v>
@@ -4353,14 +4396,14 @@
       </c>
       <c r="I22" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>76</v>
@@ -4369,22 +4412,22 @@
     </row>
     <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G23" s="10">
         <v>46100</v>
@@ -4394,14 +4437,14 @@
       </c>
       <c r="I23" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>76</v>
@@ -4410,22 +4453,22 @@
     </row>
     <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G24" s="10">
         <v>46100</v>
@@ -4435,14 +4478,14 @@
       </c>
       <c r="I24" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>76</v>
@@ -4451,22 +4494,22 @@
     </row>
     <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G25" s="10">
         <v>46100</v>
@@ -4476,14 +4519,14 @@
       </c>
       <c r="I25" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>76</v>
@@ -4492,22 +4535,22 @@
     </row>
     <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G26" s="10">
         <v>46100</v>
@@ -4517,14 +4560,14 @@
       </c>
       <c r="I26" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J26" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>76</v>
@@ -4533,22 +4576,22 @@
     </row>
     <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G27" s="10">
         <v>46100</v>
@@ -4558,14 +4601,14 @@
       </c>
       <c r="I27" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J27" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="L27" s="7" t="s">
         <v>76</v>
@@ -4574,22 +4617,22 @@
     </row>
     <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G28" s="10">
         <v>46100</v>
@@ -4599,14 +4642,14 @@
       </c>
       <c r="I28" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J28" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>76</v>
@@ -4615,22 +4658,22 @@
     </row>
     <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>95</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G29" s="10">
         <v>46100</v>
@@ -4640,14 +4683,14 @@
       </c>
       <c r="I29" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="J29" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
         <v>On track</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>76</v>
@@ -4656,16 +4699,16 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>95</v>
@@ -4681,14 +4724,14 @@
       </c>
       <c r="I30" s="7">
         <f t="shared" ref="I30:I42" ca="1" si="3">IFERROR(H30-TODAY(),"")</f>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J30" s="13" t="str">
         <f t="shared" ref="J30:J42" ca="1" si="4">IFERROR(IF(H30="","",IF(H30&lt;TODAY(),"OVERDUE",IF(H30-TODAY()&lt;=14,"Expires in 14 days",IF(H30-TODAY()&lt;=30,"Due within 30 days","On track")))),"On track")</f>
         <v>On track</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>54</v>
@@ -4697,16 +4740,16 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>95</v>
@@ -4722,14 +4765,14 @@
       </c>
       <c r="I31" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J31" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>54</v>
@@ -4738,16 +4781,16 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>95</v>
@@ -4763,14 +4806,14 @@
       </c>
       <c r="I32" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J32" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L32" s="7" t="s">
         <v>54</v>
@@ -4779,16 +4822,16 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>95</v>
@@ -4804,14 +4847,14 @@
       </c>
       <c r="I33" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J33" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>54</v>
@@ -4820,16 +4863,16 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>95</v>
@@ -4845,14 +4888,14 @@
       </c>
       <c r="I34" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J34" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>54</v>
@@ -4861,16 +4904,16 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>95</v>
@@ -4886,14 +4929,14 @@
       </c>
       <c r="I35" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J35" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>54</v>
@@ -4902,16 +4945,16 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C36" s="29" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>95</v>
@@ -4927,14 +4970,14 @@
       </c>
       <c r="I36" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J36" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>54</v>
@@ -4943,16 +4986,16 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>95</v>
@@ -4968,14 +5011,14 @@
       </c>
       <c r="I37" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J37" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L37" s="7" t="s">
         <v>54</v>
@@ -4984,16 +5027,16 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>95</v>
@@ -5009,14 +5052,14 @@
       </c>
       <c r="I38" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J38" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L38" s="7" t="s">
         <v>54</v>
@@ -5025,16 +5068,16 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>95</v>
@@ -5050,14 +5093,14 @@
       </c>
       <c r="I39" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J39" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L39" s="7" t="s">
         <v>54</v>
@@ -5066,16 +5109,16 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>95</v>
@@ -5091,14 +5134,14 @@
       </c>
       <c r="I40" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J40" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>54</v>
@@ -5107,16 +5150,16 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>95</v>
@@ -5132,14 +5175,14 @@
       </c>
       <c r="I41" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J41" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L41" s="7" t="s">
         <v>54</v>
@@ -5148,16 +5191,16 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>95</v>
@@ -5173,14 +5216,14 @@
       </c>
       <c r="I42" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J42" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>On track</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L42" s="7" t="s">
         <v>54</v>
@@ -5986,44 +6029,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -6091,14 +6134,14 @@
       </c>
       <c r="H4" s="16">
         <f t="shared" ref="H4:H34" ca="1" si="0">IFERROR(IF(G4="","",G4-TODAY()),"")</f>
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="I4" s="13" t="str">
         <f t="shared" ref="I4:I34" ca="1" si="1">IFERROR(IF(G4="","Not yet granted",IF(G4&lt;TODAY(),"EXPIRED",IF(G4-TODAY()&lt;=14,"Expires in 14 days",IF(G4-TODAY()&lt;=30,"Review within 30 days","Active")))),"Not yet granted")</f>
         <v>Active</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>119</v>
@@ -6118,7 +6161,7 @@
         <v>77</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>50</v>
@@ -6134,14 +6177,14 @@
       </c>
       <c r="H5" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="I5" s="14" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Active</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>119</v>
@@ -8191,44 +8234,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -8292,10 +8335,10 @@
         <v>133</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>142</v>
+        <v>312</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>134</v>
@@ -8314,7 +8357,7 @@
         <v>576</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N4" s="7"/>
     </row>
@@ -8330,22 +8373,22 @@
         <v>Market Street</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>133</v>
       </c>
       <c r="F5" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="J5" s="20">
         <v>320</v>
@@ -8358,13 +8401,13 @@
         <v>384</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>55</v>
@@ -8380,16 +8423,16 @@
         <v>133</v>
       </c>
       <c r="F6" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="J6" s="19">
         <v>210</v>
@@ -8402,13 +8445,13 @@
         <v>252</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N6" s="7"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>58</v>
@@ -8418,22 +8461,22 @@
         <v>Thorngrove Lodge</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>142</v>
+      <c r="F7" s="7" t="s">
+        <v>314</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H7" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>148</v>
       </c>
       <c r="J7" s="20">
         <v>560</v>
@@ -8446,13 +8489,13 @@
         <v>672</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N7" s="9"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>50</v>
@@ -8462,22 +8505,22 @@
         <v>Market Street</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="J8" s="19">
         <v>145</v>
@@ -8490,13 +8533,13 @@
         <v>174</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N8" s="7"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>55</v>
@@ -8506,22 +8549,22 @@
         <v>404 Romford Road</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>154</v>
+      <c r="F9" s="33" t="s">
+        <v>316</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J9" s="20">
         <v>400</v>
@@ -8534,17 +8577,67 @@
         <v>480</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N9" s="9"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="L10" s="21">
+      <c r="A10" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="9" t="str">
+        <f>IFERROR(INDEX(Facilities!B:B,MATCH(B10,Facilities!A:A,0)),"")</f>
+        <v>Thorngrove Lodge</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2025</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="L10" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="M10" s="9" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="9" t="str">
+        <f>IFERROR(INDEX(Facilities!B:B,MATCH(B11,Facilities!A:A,0)),"")</f>
+        <v>St. Stephens Lodge</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>324</v>
+      </c>
       <c r="L11" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -11484,6 +11577,7 @@
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="D4:D500" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"January,February,March,April,May,June,July,August,September,October,November,December"</formula1>
@@ -11513,29 +11607,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
+      <c r="A1" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>50</v>
@@ -11547,12 +11641,12 @@
         <v>58</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B5" s="23">
         <f>COUNTIF('Support Plans'!D:D,"FAC-001")</f>
@@ -11573,7 +11667,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B6" s="24">
         <f ca="1">COUNTIFS('Support Plans'!D:D,"FAC-001",'Support Plans'!J:J,"On track")</f>
@@ -11594,7 +11688,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B7" s="23">
         <f ca="1">COUNTIFS('Support Plans'!D:D,"FAC-001",'Support Plans'!J:J,"Due within 30 days")</f>
@@ -11615,7 +11709,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B8" s="24">
         <f ca="1">COUNTIFS('Support Plans'!D:D,"FAC-001",'Support Plans'!J:J,"OVERDUE")</f>
@@ -11635,17 +11729,17 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
+      <c r="A9" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>50</v>
@@ -11657,7 +11751,7 @@
         <v>58</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -11683,7 +11777,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B12" s="24">
         <f ca="1">COUNTIFS(DoLS!D:D,"FAC-001",DoLS!I:I,"Review within 30 days")</f>
@@ -11704,7 +11798,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B13" s="23">
         <f ca="1">COUNTIFS(DoLS!D:D,"FAC-001",DoLS!I:I,"Expires in 14 days")</f>
@@ -11725,7 +11819,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B14" s="24">
         <f ca="1">COUNTIFS(DoLS!D:D,"FAC-001",DoLS!I:I,"EXPIRED")</f>
@@ -11745,17 +11839,17 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
+      <c r="A15" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>50</v>
@@ -11767,12 +11861,12 @@
         <v>58</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B17" s="25">
         <f>SUMIF(Expenses!B:B,"FAC-001",Expenses!L:L)</f>
@@ -11793,7 +11887,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B18" s="27">
         <f>SUMIFS(Expenses!L:L,Expenses!B:B,"FAC-001",Expenses!F:F,"Staffing")</f>
@@ -11814,11 +11908,11 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B19" s="25">
         <f>SUMIFS(Expenses!L:L,Expenses!B:B,"FAC-001",Expenses!F:F,"Utilities")</f>
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="C19" s="25">
         <f>SUMIFS(Expenses!L:L,Expenses!B:B,"FAC-002",Expenses!F:F,"Utilities")</f>
@@ -11830,16 +11924,16 @@
       </c>
       <c r="E19" s="26">
         <f>SUM(B19:D19)</f>
-        <v>384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B20" s="27">
         <f>SUMIFS(Expenses!L:L,Expenses!B:B,"FAC-001",Expenses!F:F,"Maintenance")</f>
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="C20" s="27">
         <f>SUMIFS(Expenses!L:L,Expenses!B:B,"FAC-002",Expenses!F:F,"Maintenance")</f>
@@ -11847,11 +11941,11 @@
       </c>
       <c r="D20" s="27">
         <f>SUMIFS(Expenses!L:L,Expenses!B:B,"FAC-003",Expenses!F:F,"Maintenance")</f>
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="E20" s="28">
         <f>SUM(B20:D20)</f>
-        <v>1500</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
